--- a/docs/finanzen/Kosten_Prognose.xlsx
+++ b/docs/finanzen/Kosten_Prognose.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PCUser\Documents\Projekte\mini-climate-control\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PCUser\Documents\Projekte\mini-climate-control\docs\finanzen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7A1E111-8336-4E71-9FE2-2F3E54041E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9638D480-1C5F-493E-85EA-655BCDCBD54F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1073" yWindow="1073" windowWidth="21600" windowHeight="11872" xr2:uid="{9A33E93A-2FFC-4E05-A037-0ECCD8CDDAF5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
   <si>
     <t>Kostenprognose Diplomarbeit SCC-2109</t>
   </si>
@@ -50,20 +50,80 @@
     <t>Hauptplatine</t>
   </si>
   <si>
-    <t>Sensorplatine</t>
-  </si>
-  <si>
     <t>Modellraum</t>
   </si>
   <si>
-    <t>~200€</t>
+    <t>Produkt</t>
+  </si>
+  <si>
+    <t>Kosten (vorraussichtlich)</t>
+  </si>
+  <si>
+    <t>~200-250€</t>
+  </si>
+  <si>
+    <t>~30€</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/Thermoelektrischer-Halbleiterk%C3%BChlung-Thermoelektrisches-Entfeuchtungssystem-Praktikabilit%C3%A4t/dp/B08HZC5KZJ?source=ps-sl-shoppingads-lpcontext&amp;ref_=fplfs&amp;psc=1&amp;shipTo=AT&amp;language=de_DE&amp;smid=AFB530CH8NFSI</t>
+  </si>
+  <si>
+    <t>Sensorplatinen</t>
+  </si>
+  <si>
+    <t>Thermoelektr. Heiz-/Kühlsystem</t>
+  </si>
+  <si>
+    <t>4-Pin Lüfter</t>
+  </si>
+  <si>
+    <t>Anzahl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/GDSTIME-Hochdruck-K%C3%BChlventilator-Dual-Kugellager-L%C3%BCfter/dp/B08JPYKYTS/ref=sr_1_1_sspa?__mk_de_DE=%C3%85M%C3%85%C5%BD%C3%95%C3%91&amp;crid=23TZGJLFCJUS7&amp;dib=eyJ2IjoiMSJ9.7a556LAEYBbd7gAD7c1RT1O7LEMVGCz3oY7FXEb1HQvuq6AKqE6GRfmBykVqxmVYGbEvdhYgXQaxjSIx4zaRxgTiJasJrfjqGlxEvinKGK8i3pGfinU3NnZeMWU5VAAATuTjIQOidBtQ73bza4TU-rIopKuhQmJegu7Qkdey6TidSR-VuEiwNVjjLq3WuD7FxA4j8NReiHDkq6UnMbpLGtPCuGuz1qnra2LOKwcRKE7TZDxIaDbTxtfb7YiFg6jfeEv-6qIHIabF6k3Vz_tA7Xvk3knMjqBoW1V5Iqp6vb8.59j6M4zHJcF339_Efbp3tUzwBJZ8f5hZFBt4vhVM2WA&amp;dib_tag=se&amp;keywords=pwm%2Bfan%2B4pin&amp;qid=1784919877&amp;s=industrial&amp;sprefix=pwm%2Bfan%2B4pin%2Cindustrial%2C107&amp;sr=1-1-spons&amp;aref=zysyMygifK&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
+  </si>
+  <si>
+    <t>12V-Netzteil</t>
+  </si>
+  <si>
+    <t>~25€</t>
+  </si>
+  <si>
+    <t>Bauteile (beide Platinen)</t>
+  </si>
+  <si>
+    <t>~50-60€</t>
+  </si>
+  <si>
+    <t>ges:</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/Jippofu-100V-240V-Bildschirm-Lautsprecher-Transformator/dp/B0FGV1ZBDT/ref=sr_1_1_sspa?crid=12ECIAT2RCDW7&amp;dib=eyJ2IjoiMSJ9.qEDPw93salMSTRWQS0jQJdZw1OTx74ygZ_zi5ZZMxg0MDdMlCvOa0Q5BlbfRHOH_MOo-p3YGDu1FRaELMMcjSbCOEeJquwscGiIPx573jkQQtbwTrIX-W4PPIu5luBod9NE4wu62mGJnWMVx7KYjAbxWG1ubk8pinAQYCJi7P4oJZkd6GEfAdbDsd8fVJnE1ujxxWbnxn5fFjjXUpdfkSdpwT41mPXteFAHgnA-M8blPu6k8sTYNnrksL2jJh70VpCwXPQECEzUxELmcjgcW2lPoVkV5NVYdmd-5_9XLXxo.i2VaQQRM9_w0no523BLqtzvnONtb3fhPCSCwiJJMbkM&amp;dib_tag=se&amp;keywords=12v%2B10a%2Bnetzteil%2Badapter&amp;qid=1789997166&amp;sprefix=12V%2B10a%2Bne%2Caps%2C120&amp;sr=8-1-spons&amp;aref=RipI0Qkki8&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
+  </si>
+  <si>
+    <t>~365€-425€</t>
+  </si>
+  <si>
+    <t>1x</t>
+  </si>
+  <si>
+    <t>2x</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>n.V.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -71,16 +131,60 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -88,14 +192,184 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -428,42 +702,146 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E167685E-88B8-427D-B1F2-3012ADA46F04}">
-  <dimension ref="B3:C7"/>
+  <dimension ref="A3:D13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="2" max="2" width="28.265625" customWidth="1"/>
+    <col min="3" max="3" width="22.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B3" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B5" t="s">
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B6" t="s">
+      <c r="D6" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
-        <v>5</v>
+      <c r="C8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D9" r:id="rId1" xr:uid="{7A5E0E84-F695-4E10-8FF5-BE6F222F91B5}"/>
+    <hyperlink ref="D10" r:id="rId2" display="https://www.amazon.de/GDSTIME-Hochdruck-K%C3%BChlventilator-Dual-Kugellager-L%C3%BCfter/dp/B08JPYKYTS/ref=sr_1_1_sspa?__mk_de_DE=%C3%85M%C3%85%C5%BD%C3%95%C3%91&amp;crid=23TZGJLFCJUS7&amp;dib=eyJ2IjoiMSJ9.7a556LAEYBbd7gAD7c1RT1O7LEMVGCz3oY7FXEb1HQvuq6AKqE6GRfmBykVqxmVYGbEvdhYgXQaxjSIx4zaRxgTiJasJrfjqGlxEvinKGK8i3pGfinU3NnZeMWU5VAAATuTjIQOidBtQ73bza4TU-rIopKuhQmJegu7Qkdey6TidSR-VuEiwNVjjLq3WuD7FxA4j8NReiHDkq6UnMbpLGtPCuGuz1qnra2LOKwcRKE7TZDxIaDbTxtfb7YiFg6jfeEv-6qIHIabF6k3Vz_tA7Xvk3knMjqBoW1V5Iqp6vb8.59j6M4zHJcF339_Efbp3tUzwBJZ8f5hZFBt4vhVM2WA&amp;dib_tag=se&amp;keywords=pwm%2Bfan%2B4pin&amp;qid=1784919877&amp;s=industrial&amp;sprefix=pwm%2Bfan%2B4pin%2Cindustrial%2C107&amp;sr=1-1-spons&amp;aref=zysyMygifK&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1" xr:uid="{8DA6CDA0-277F-4581-93B9-41F16BB502E2}"/>
+    <hyperlink ref="D11" r:id="rId3" display="https://www.amazon.de/Jippofu-100V-240V-Bildschirm-Lautsprecher-Transformator/dp/B0FGV1ZBDT/ref=sr_1_1_sspa?crid=12ECIAT2RCDW7&amp;dib=eyJ2IjoiMSJ9.qEDPw93salMSTRWQS0jQJdZw1OTx74ygZ_zi5ZZMxg0MDdMlCvOa0Q5BlbfRHOH_MOo-p3YGDu1FRaELMMcjSbCOEeJquwscGiIPx573jkQQtbwTrIX-W4PPIu5luBod9NE4wu62mGJnWMVx7KYjAbxWG1ubk8pinAQYCJi7P4oJZkd6GEfAdbDsd8fVJnE1ujxxWbnxn5fFjjXUpdfkSdpwT41mPXteFAHgnA-M8blPu6k8sTYNnrksL2jJh70VpCwXPQECEzUxELmcjgcW2lPoVkV5NVYdmd-5_9XLXxo.i2VaQQRM9_w0no523BLqtzvnONtb3fhPCSCwiJJMbkM&amp;dib_tag=se&amp;keywords=12v%2B10a%2Bnetzteil%2Badapter&amp;qid=1789997166&amp;sprefix=12V%2B10a%2Bne%2Caps%2C120&amp;sr=8-1-spons&amp;aref=RipI0Qkki8&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1" xr:uid="{817D3A8F-39EE-4CB9-A91E-3A1FED27720F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>